--- a/data/nzd0177/nzd0177.xlsx
+++ b/data/nzd0177/nzd0177.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J357"/>
+  <dimension ref="A1:J359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13290,6 +13290,78 @@
       <c r="J357" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>370.97</v>
+      </c>
+      <c r="C358" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="D358" t="n">
+        <v>366.34</v>
+      </c>
+      <c r="E358" t="n">
+        <v>369.62</v>
+      </c>
+      <c r="F358" t="n">
+        <v>369.2</v>
+      </c>
+      <c r="G358" t="n">
+        <v>375.21</v>
+      </c>
+      <c r="H358" t="n">
+        <v>367.28</v>
+      </c>
+      <c r="I358" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="C359" t="n">
+        <v>365.24</v>
+      </c>
+      <c r="D359" t="n">
+        <v>366.14</v>
+      </c>
+      <c r="E359" t="n">
+        <v>370.01</v>
+      </c>
+      <c r="F359" t="n">
+        <v>368.88</v>
+      </c>
+      <c r="G359" t="n">
+        <v>374.37</v>
+      </c>
+      <c r="H359" t="n">
+        <v>364.43</v>
+      </c>
+      <c r="I359" t="n">
+        <v>368.05</v>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B367"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16977,6 +17049,26 @@
       </c>
       <c r="B367" t="n">
         <v>-0.4</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -17145,28 +17237,28 @@
         <v>0.1672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3348896484912345</v>
+        <v>0.333191382079321</v>
       </c>
       <c r="J2" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K2" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1777714084690563</v>
+        <v>0.1780832775418372</v>
       </c>
       <c r="M2" t="n">
-        <v>4.242871756609437</v>
+        <v>4.225405295205109</v>
       </c>
       <c r="N2" t="n">
-        <v>28.16476653901432</v>
+        <v>28.02139627370417</v>
       </c>
       <c r="O2" t="n">
-        <v>5.307048759811268</v>
+        <v>5.29352399387253</v>
       </c>
       <c r="P2" t="n">
-        <v>363.0669548518244</v>
+        <v>363.0845556067767</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17227,28 +17319,28 @@
         <v>0.1707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2562348450874662</v>
+        <v>0.2563824808687492</v>
       </c>
       <c r="J3" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1751447478668677</v>
+        <v>0.1771589125678275</v>
       </c>
       <c r="M3" t="n">
-        <v>3.204566319026273</v>
+        <v>3.189269803357063</v>
       </c>
       <c r="N3" t="n">
-        <v>16.78916317502484</v>
+        <v>16.69656876208964</v>
       </c>
       <c r="O3" t="n">
-        <v>4.097458135847741</v>
+        <v>4.086143507280384</v>
       </c>
       <c r="P3" t="n">
-        <v>358.7834924828022</v>
+        <v>358.7819651063501</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17309,28 +17401,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2196516791386165</v>
+        <v>0.2189894425212075</v>
       </c>
       <c r="J4" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K4" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.13923675584048</v>
+        <v>0.140034561678875</v>
       </c>
       <c r="M4" t="n">
-        <v>3.13064962699337</v>
+        <v>3.116366701148086</v>
       </c>
       <c r="N4" t="n">
-        <v>16.19462590562569</v>
+        <v>16.10607409188766</v>
       </c>
       <c r="O4" t="n">
-        <v>4.024254701882784</v>
+        <v>4.013237358030006</v>
       </c>
       <c r="P4" t="n">
-        <v>361.0252786099217</v>
+        <v>361.0321413717221</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17391,28 +17483,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.125958232869775</v>
+        <v>0.1251172357830374</v>
       </c>
       <c r="J5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06635470127551979</v>
+        <v>0.06630109101900217</v>
       </c>
       <c r="M5" t="n">
-        <v>2.811182386993665</v>
+        <v>2.800007520148113</v>
       </c>
       <c r="N5" t="n">
-        <v>12.12091433190951</v>
+        <v>12.05641069904914</v>
       </c>
       <c r="O5" t="n">
-        <v>3.481510352118677</v>
+        <v>3.472234251753349</v>
       </c>
       <c r="P5" t="n">
-        <v>367.2263547140295</v>
+        <v>367.2350681923846</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -17473,28 +17565,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03516743882606339</v>
+        <v>0.0355701445827162</v>
       </c>
       <c r="J6" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K6" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002876092906009098</v>
+        <v>0.002979988866732008</v>
       </c>
       <c r="M6" t="n">
-        <v>3.683074011992406</v>
+        <v>3.664226672135551</v>
       </c>
       <c r="N6" t="n">
-        <v>23.06609461103121</v>
+        <v>22.93769973998876</v>
       </c>
       <c r="O6" t="n">
-        <v>4.802717419444039</v>
+        <v>4.789331867806694</v>
       </c>
       <c r="P6" t="n">
-        <v>367.7615287677218</v>
+        <v>367.757328923093</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -17555,28 +17647,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1384056825608903</v>
+        <v>-0.1303989485975694</v>
       </c>
       <c r="J7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K7" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03478775706184933</v>
+        <v>0.03110334214950705</v>
       </c>
       <c r="M7" t="n">
-        <v>4.395327090998824</v>
+        <v>4.408591126471198</v>
       </c>
       <c r="N7" t="n">
-        <v>28.59239966815806</v>
+        <v>28.70172165263597</v>
       </c>
       <c r="O7" t="n">
-        <v>5.347186144895095</v>
+        <v>5.357398776704603</v>
       </c>
       <c r="P7" t="n">
-        <v>371.4595897036614</v>
+        <v>371.3760714304089</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17637,28 +17729,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1658792309792862</v>
+        <v>-0.1616047913331107</v>
       </c>
       <c r="J8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K8" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05023862579924199</v>
+        <v>0.04824849964157363</v>
       </c>
       <c r="M8" t="n">
-        <v>4.367370239281167</v>
+        <v>4.364852844215985</v>
       </c>
       <c r="N8" t="n">
-        <v>27.98382962524516</v>
+        <v>27.91499740156562</v>
       </c>
       <c r="O8" t="n">
-        <v>5.289974444668439</v>
+        <v>5.283464526384711</v>
       </c>
       <c r="P8" t="n">
-        <v>366.5025023137476</v>
+        <v>366.4579222648574</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -17719,28 +17811,28 @@
         <v>0.1442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1322530739318191</v>
+        <v>-0.1290313638810333</v>
       </c>
       <c r="J9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03710362328738581</v>
+        <v>0.03572836564574589</v>
       </c>
       <c r="M9" t="n">
-        <v>3.972105642633995</v>
+        <v>3.96527793883052</v>
       </c>
       <c r="N9" t="n">
-        <v>24.64602177735864</v>
+        <v>24.57391729588434</v>
       </c>
       <c r="O9" t="n">
-        <v>4.964475982151454</v>
+        <v>4.95720861936275</v>
       </c>
       <c r="P9" t="n">
-        <v>370.6683840404326</v>
+        <v>370.6350109817155</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -17782,7 +17874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J357"/>
+  <dimension ref="A1:J359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36337,6 +36429,110 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-36.82715213695923,175.71492534782377</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-36.827810380701365,175.71529743294593</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-36.828461038874,175.7156812042518</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-36.82908593416826,175.71610712250904</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-36.82967971079576,175.71659359399868</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-36.83019859370251,175.71718040903784</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-36.83069549613107,175.71780637704018</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-36.831065034732944,175.7185730285051</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-36.82715695657313,175.71491444990514</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-36.82781403821398,175.71528868431153</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-36.82846184914561,175.7156792025526</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-36.82908412643507,175.7161108698268</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-36.829681435459364,175.71659072071992</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-36.83020398836451,175.7171738083194</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-36.83071635193927,175.71778775241452</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-36.83109451515224,175.71854884756598</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0177/nzd0177.xlsx
+++ b/data/nzd0177/nzd0177.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J359"/>
+  <dimension ref="A1:J360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13362,6 +13362,42 @@
       <c r="J359" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>369.53</v>
+      </c>
+      <c r="C360" t="n">
+        <v>363.22</v>
+      </c>
+      <c r="D360" t="n">
+        <v>365.06</v>
+      </c>
+      <c r="E360" t="n">
+        <v>368.57</v>
+      </c>
+      <c r="F360" t="n">
+        <v>367.27</v>
+      </c>
+      <c r="G360" t="n">
+        <v>372.38</v>
+      </c>
+      <c r="H360" t="n">
+        <v>361.12</v>
+      </c>
+      <c r="I360" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17069,6 +17105,16 @@
       </c>
       <c r="B369" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -17237,28 +17283,28 @@
         <v>0.1672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.333191382079321</v>
+        <v>0.3318457014099902</v>
       </c>
       <c r="J2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1780832775418372</v>
+        <v>0.1777501419910624</v>
       </c>
       <c r="M2" t="n">
-        <v>4.225405295205109</v>
+        <v>4.21857474800107</v>
       </c>
       <c r="N2" t="n">
-        <v>28.02139627370417</v>
+        <v>27.95888926741449</v>
       </c>
       <c r="O2" t="n">
-        <v>5.29352399387253</v>
+        <v>5.287616596105895</v>
       </c>
       <c r="P2" t="n">
-        <v>363.0845556067767</v>
+        <v>363.0985450074774</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17319,28 +17365,28 @@
         <v>0.1707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2563824808687492</v>
+        <v>0.2550494115684904</v>
       </c>
       <c r="J3" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K3" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1771589125678275</v>
+        <v>0.1764356283399285</v>
       </c>
       <c r="M3" t="n">
-        <v>3.189269803357063</v>
+        <v>3.185798862172098</v>
       </c>
       <c r="N3" t="n">
-        <v>16.69656876208964</v>
+        <v>16.66531719652549</v>
       </c>
       <c r="O3" t="n">
-        <v>4.086143507280384</v>
+        <v>4.082317625629526</v>
       </c>
       <c r="P3" t="n">
-        <v>358.7819651063501</v>
+        <v>358.7958234020278</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17401,28 +17447,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2189894425212075</v>
+        <v>0.2179836177704692</v>
       </c>
       <c r="J4" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.140034561678875</v>
+        <v>0.1396285708763199</v>
       </c>
       <c r="M4" t="n">
-        <v>3.116366701148086</v>
+        <v>3.112507857216802</v>
       </c>
       <c r="N4" t="n">
-        <v>16.10607409188766</v>
+        <v>16.06989613587762</v>
       </c>
       <c r="O4" t="n">
-        <v>4.013237358030006</v>
+        <v>4.008727495836755</v>
       </c>
       <c r="P4" t="n">
-        <v>361.0321413717221</v>
+        <v>361.0425977049322</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17483,28 +17529,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1251172357830374</v>
+        <v>0.1239963904442778</v>
       </c>
       <c r="J5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06630109101900217</v>
+        <v>0.06553012730603824</v>
       </c>
       <c r="M5" t="n">
-        <v>2.800007520148113</v>
+        <v>2.798186884771928</v>
       </c>
       <c r="N5" t="n">
-        <v>12.05641069904914</v>
+        <v>12.03361323726952</v>
       </c>
       <c r="O5" t="n">
-        <v>3.472234251753349</v>
+        <v>3.468949875289281</v>
       </c>
       <c r="P5" t="n">
-        <v>367.2350681923846</v>
+        <v>367.2467202543669</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -17565,28 +17611,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0355701445827162</v>
+        <v>0.0347555729103223</v>
       </c>
       <c r="J6" t="n">
+        <v>359</v>
+      </c>
+      <c r="K6" t="n">
         <v>358</v>
       </c>
-      <c r="K6" t="n">
-        <v>357</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.002979988866732008</v>
+        <v>0.002862965728838152</v>
       </c>
       <c r="M6" t="n">
-        <v>3.664226672135551</v>
+        <v>3.658305067564446</v>
       </c>
       <c r="N6" t="n">
-        <v>22.93769973998876</v>
+        <v>22.87924782998477</v>
       </c>
       <c r="O6" t="n">
-        <v>4.789331867806694</v>
+        <v>4.783225672073687</v>
       </c>
       <c r="P6" t="n">
-        <v>367.757328923093</v>
+        <v>367.7658533127276</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -17647,28 +17693,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1303989485975694</v>
+        <v>-0.1278540050785881</v>
       </c>
       <c r="J7" t="n">
+        <v>359</v>
+      </c>
+      <c r="K7" t="n">
         <v>358</v>
       </c>
-      <c r="K7" t="n">
-        <v>357</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.03110334214950705</v>
+        <v>0.03006765432614</v>
       </c>
       <c r="M7" t="n">
-        <v>4.408591126471198</v>
+        <v>4.408280460361108</v>
       </c>
       <c r="N7" t="n">
-        <v>28.70172165263597</v>
+        <v>28.67640529164393</v>
       </c>
       <c r="O7" t="n">
-        <v>5.357398776704603</v>
+        <v>5.355035507972279</v>
       </c>
       <c r="P7" t="n">
-        <v>371.3760714304089</v>
+        <v>371.3494389180232</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17729,28 +17775,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1616047913331107</v>
+        <v>-0.162207047716609</v>
       </c>
       <c r="J8" t="n">
+        <v>359</v>
+      </c>
+      <c r="K8" t="n">
         <v>358</v>
       </c>
-      <c r="K8" t="n">
-        <v>357</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04824849964157363</v>
+        <v>0.04888288949207231</v>
       </c>
       <c r="M8" t="n">
-        <v>4.364852844215985</v>
+        <v>4.355425595357666</v>
       </c>
       <c r="N8" t="n">
-        <v>27.91499740156562</v>
+        <v>27.84009461791902</v>
       </c>
       <c r="O8" t="n">
-        <v>5.283464526384711</v>
+        <v>5.276371349508961</v>
       </c>
       <c r="P8" t="n">
-        <v>366.4579222648574</v>
+        <v>366.4642248018187</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -17811,28 +17857,28 @@
         <v>0.1442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1290313638810333</v>
+        <v>-0.1312132847284963</v>
       </c>
       <c r="J9" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K9" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03572836564574589</v>
+        <v>0.03706956245094062</v>
       </c>
       <c r="M9" t="n">
-        <v>3.96527793883052</v>
+        <v>3.965176783025103</v>
       </c>
       <c r="N9" t="n">
-        <v>24.57391729588434</v>
+        <v>24.54633971163324</v>
       </c>
       <c r="O9" t="n">
-        <v>4.95720861936275</v>
+        <v>4.954426274719732</v>
       </c>
       <c r="P9" t="n">
-        <v>370.6350109817155</v>
+        <v>370.6576937516535</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -17874,7 +17920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J359"/>
+  <dimension ref="A1:J360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36533,6 +36579,58 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-36.82715838943112,175.7149112099831</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-36.82782243386561,175.71526860221567</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-36.82846622461171,175.71566839337595</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-36.82909080114168,175.71609703357578</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-36.82969011267216,175.71657626453407</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-36.83021676857437,175.71715817089932</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-36.83074057394487,175.71776612169646</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-36.8311297111574,175.71851997846184</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0177/nzd0177.xlsx
+++ b/data/nzd0177/nzd0177.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J360"/>
+  <dimension ref="A1:J362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13396,6 +13396,78 @@
         <v>363.37</v>
       </c>
       <c r="J360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>368.87</v>
+      </c>
+      <c r="C361" t="n">
+        <v>364.73</v>
+      </c>
+      <c r="D361" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="E361" t="n">
+        <v>369.05</v>
+      </c>
+      <c r="F361" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="G361" t="n">
+        <v>369.88</v>
+      </c>
+      <c r="H361" t="n">
+        <v>358.52</v>
+      </c>
+      <c r="I361" t="n">
+        <v>364.06</v>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>370.11</v>
+      </c>
+      <c r="C362" t="n">
+        <v>366.85</v>
+      </c>
+      <c r="D362" t="n">
+        <v>366.88</v>
+      </c>
+      <c r="E362" t="n">
+        <v>369.75</v>
+      </c>
+      <c r="F362" t="n">
+        <v>367.64</v>
+      </c>
+      <c r="G362" t="n">
+        <v>371.77</v>
+      </c>
+      <c r="H362" t="n">
+        <v>360.46</v>
+      </c>
+      <c r="I362" t="n">
+        <v>364.66</v>
+      </c>
+      <c r="J362" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13412,7 +13484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B370"/>
+  <dimension ref="A1:B372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17115,6 +17187,26 @@
       </c>
       <c r="B370" t="n">
         <v>0.53</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -17283,28 +17375,28 @@
         <v>0.1672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3318457014099902</v>
+        <v>0.3291324427281441</v>
       </c>
       <c r="J2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1777501419910624</v>
+        <v>0.177027883196177</v>
       </c>
       <c r="M2" t="n">
-        <v>4.21857474800107</v>
+        <v>4.205083273956577</v>
       </c>
       <c r="N2" t="n">
-        <v>27.95888926741449</v>
+        <v>27.83796985062364</v>
       </c>
       <c r="O2" t="n">
-        <v>5.287616596105895</v>
+        <v>5.276169998268028</v>
       </c>
       <c r="P2" t="n">
-        <v>363.0985450074774</v>
+        <v>363.1268389507647</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17365,28 +17457,28 @@
         <v>0.1707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2550494115684904</v>
+        <v>0.255301308994012</v>
       </c>
       <c r="J3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1764356283399285</v>
+        <v>0.1785197210859601</v>
       </c>
       <c r="M3" t="n">
-        <v>3.185798862172098</v>
+        <v>3.174211412679121</v>
       </c>
       <c r="N3" t="n">
-        <v>16.66531719652549</v>
+        <v>16.57943608077036</v>
       </c>
       <c r="O3" t="n">
-        <v>4.082317625629526</v>
+        <v>4.071785367718977</v>
       </c>
       <c r="P3" t="n">
-        <v>358.7958234020278</v>
+        <v>358.7931905717204</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17447,28 +17539,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2179836177704692</v>
+        <v>0.2171466254991526</v>
       </c>
       <c r="J4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1396285708763199</v>
+        <v>0.1401807710137256</v>
       </c>
       <c r="M4" t="n">
-        <v>3.112507857216802</v>
+        <v>3.099600531220243</v>
       </c>
       <c r="N4" t="n">
-        <v>16.06989613587762</v>
+        <v>15.98739142067793</v>
       </c>
       <c r="O4" t="n">
-        <v>4.008727495836755</v>
+        <v>3.998423616961806</v>
       </c>
       <c r="P4" t="n">
-        <v>361.0425977049322</v>
+        <v>361.0513226127699</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17529,28 +17621,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1239963904442778</v>
+        <v>0.1227182086399112</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K5" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06553012730603824</v>
+        <v>0.06500057175906648</v>
       </c>
       <c r="M5" t="n">
-        <v>2.798186884771928</v>
+        <v>2.78942129723508</v>
       </c>
       <c r="N5" t="n">
-        <v>12.03361323726952</v>
+        <v>11.9747074492432</v>
       </c>
       <c r="O5" t="n">
-        <v>3.468949875289281</v>
+        <v>3.460449024222609</v>
       </c>
       <c r="P5" t="n">
-        <v>367.2467202543669</v>
+        <v>367.2600488354397</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -17611,28 +17703,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0347555729103223</v>
+        <v>0.03249253242234103</v>
       </c>
       <c r="J6" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K6" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002862965728838152</v>
+        <v>0.00253220937182963</v>
       </c>
       <c r="M6" t="n">
-        <v>3.658305067564446</v>
+        <v>3.649827966894897</v>
       </c>
       <c r="N6" t="n">
-        <v>22.87924782998477</v>
+        <v>22.77911429422241</v>
       </c>
       <c r="O6" t="n">
-        <v>4.783225672073687</v>
+        <v>4.772747038574579</v>
       </c>
       <c r="P6" t="n">
-        <v>367.7658533127276</v>
+        <v>367.7896061709097</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -17693,28 +17785,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1278540050785881</v>
+        <v>-0.1246041763673585</v>
       </c>
       <c r="J7" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K7" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03006765432614</v>
+        <v>0.02890874831086099</v>
       </c>
       <c r="M7" t="n">
-        <v>4.408280460361108</v>
+        <v>4.398977287778727</v>
       </c>
       <c r="N7" t="n">
-        <v>28.67640529164393</v>
+        <v>28.56711572989578</v>
       </c>
       <c r="O7" t="n">
-        <v>5.355035507972279</v>
+        <v>5.344821393638498</v>
       </c>
       <c r="P7" t="n">
-        <v>371.3494389180232</v>
+        <v>371.3153160776878</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17775,28 +17867,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.162207047716609</v>
+        <v>-0.1652179212778972</v>
       </c>
       <c r="J8" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K8" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04888288949207231</v>
+        <v>0.05116076758503907</v>
       </c>
       <c r="M8" t="n">
-        <v>4.355425595357666</v>
+        <v>4.344903756551721</v>
       </c>
       <c r="N8" t="n">
-        <v>27.84009461791902</v>
+        <v>27.7293910249379</v>
       </c>
       <c r="O8" t="n">
-        <v>5.276371349508961</v>
+        <v>5.26587039575965</v>
       </c>
       <c r="P8" t="n">
-        <v>366.4642248018187</v>
+        <v>366.495828564366</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -17857,28 +17949,28 @@
         <v>0.1442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1312132847284963</v>
+        <v>-0.1343676774118439</v>
       </c>
       <c r="J9" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K9" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03706956245094062</v>
+        <v>0.03921218118365244</v>
       </c>
       <c r="M9" t="n">
-        <v>3.965176783025103</v>
+        <v>3.958883883231866</v>
       </c>
       <c r="N9" t="n">
-        <v>24.54633971163324</v>
+        <v>24.45393973823878</v>
       </c>
       <c r="O9" t="n">
-        <v>4.954426274719732</v>
+        <v>4.945092490362417</v>
       </c>
       <c r="P9" t="n">
-        <v>370.6576937516535</v>
+        <v>370.6905900781457</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -17920,7 +18012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J360"/>
+  <dimension ref="A1:J362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36631,6 +36723,110 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-36.82716125514687,175.71490473013864</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-36.827816157908515,175.71528361407982</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-36.828465292799564,175.71567069533035</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-36.82908857623964,175.71610164565973</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-36.829698412613304,175.71656243687497</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-36.830232824111754,175.71713852589187</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-36.830759600291245,175.71774913079065</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-36.83112452200319,175.71852423480576</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-36.82715587107457,175.71491690439143</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-36.827807346627935,175.71530469033516</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-36.82845885114052,175.71568660883952</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-36.829085331590534,175.71610837161498</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-36.82968811853023,175.7165795867634</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-36.83022068612577,175.71715337751826</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-36.83074540370991,175.71776180862116</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-36.831120009695056,175.71852793597392</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0177/nzd0177.xlsx
+++ b/data/nzd0177/nzd0177.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J362"/>
+  <dimension ref="A1:J363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13468,6 +13468,42 @@
         <v>364.66</v>
       </c>
       <c r="J362" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>370.97</v>
+      </c>
+      <c r="C363" t="n">
+        <v>366.9</v>
+      </c>
+      <c r="D363" t="n">
+        <v>367.59</v>
+      </c>
+      <c r="E363" t="n">
+        <v>370.35</v>
+      </c>
+      <c r="F363" t="n">
+        <v>368.81</v>
+      </c>
+      <c r="G363" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="H363" t="n">
+        <v>360.37</v>
+      </c>
+      <c r="I363" t="n">
+        <v>365.6</v>
+      </c>
+      <c r="J363" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13484,7 +13520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B372"/>
+  <dimension ref="A1:B373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17207,6 +17243,16 @@
       </c>
       <c r="B372" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -17375,28 +17421,28 @@
         <v>0.1672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3291324427281441</v>
+        <v>0.3286198869067201</v>
       </c>
       <c r="J2" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K2" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.177027883196177</v>
+        <v>0.1774792004119369</v>
       </c>
       <c r="M2" t="n">
-        <v>4.205083273956577</v>
+        <v>4.195335440776939</v>
       </c>
       <c r="N2" t="n">
-        <v>27.83796985062364</v>
+        <v>27.76337726330272</v>
       </c>
       <c r="O2" t="n">
-        <v>5.276169998268028</v>
+        <v>5.269096437085083</v>
       </c>
       <c r="P2" t="n">
-        <v>363.1268389507647</v>
+        <v>363.132196866952</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17457,28 +17503,28 @@
         <v>0.1707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.255301308994012</v>
+        <v>0.2560334287717259</v>
       </c>
       <c r="J3" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K3" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1785197210859601</v>
+        <v>0.1802474924724576</v>
       </c>
       <c r="M3" t="n">
-        <v>3.174211412679121</v>
+        <v>3.169651104549347</v>
       </c>
       <c r="N3" t="n">
-        <v>16.57943608077036</v>
+        <v>16.53834517388024</v>
       </c>
       <c r="O3" t="n">
-        <v>4.071785367718977</v>
+        <v>4.066736427884187</v>
       </c>
       <c r="P3" t="n">
-        <v>358.7931905717204</v>
+        <v>358.7855374805955</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17539,28 +17585,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2171466254991526</v>
+        <v>0.2175680834773</v>
       </c>
       <c r="J4" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K4" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1401807710137256</v>
+        <v>0.1413995217425364</v>
       </c>
       <c r="M4" t="n">
-        <v>3.099600531220243</v>
+        <v>3.093123409921132</v>
       </c>
       <c r="N4" t="n">
-        <v>15.98739142067793</v>
+        <v>15.94478776982568</v>
       </c>
       <c r="O4" t="n">
-        <v>3.998423616961806</v>
+        <v>3.993092507045847</v>
       </c>
       <c r="P4" t="n">
-        <v>361.0513226127699</v>
+        <v>361.046916972586</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17621,28 +17667,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1227182086399112</v>
+        <v>0.122618668169945</v>
       </c>
       <c r="J5" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K5" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06500057175906648</v>
+        <v>0.06528464441947313</v>
       </c>
       <c r="M5" t="n">
-        <v>2.78942129723508</v>
+        <v>2.782236206493645</v>
       </c>
       <c r="N5" t="n">
-        <v>11.9747074492432</v>
+        <v>11.94171518924773</v>
       </c>
       <c r="O5" t="n">
-        <v>3.460449024222609</v>
+        <v>3.45567868721149</v>
       </c>
       <c r="P5" t="n">
-        <v>367.2600488354397</v>
+        <v>367.2610893650231</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -17703,28 +17749,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03249253242234103</v>
+        <v>0.03257734508696567</v>
       </c>
       <c r="J6" t="n">
+        <v>362</v>
+      </c>
+      <c r="K6" t="n">
         <v>361</v>
       </c>
-      <c r="K6" t="n">
-        <v>360</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.00253220937182963</v>
+        <v>0.002561507041678901</v>
       </c>
       <c r="M6" t="n">
-        <v>3.649827966894897</v>
+        <v>3.640104496939608</v>
       </c>
       <c r="N6" t="n">
-        <v>22.77911429422241</v>
+        <v>22.71607659948119</v>
       </c>
       <c r="O6" t="n">
-        <v>4.772747038574579</v>
+        <v>4.766138541784239</v>
       </c>
       <c r="P6" t="n">
-        <v>367.7896061709097</v>
+        <v>367.7887137435646</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -17785,28 +17831,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1246041763673585</v>
+        <v>-0.1219925597992143</v>
       </c>
       <c r="J7" t="n">
+        <v>362</v>
+      </c>
+      <c r="K7" t="n">
         <v>361</v>
       </c>
-      <c r="K7" t="n">
-        <v>360</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02890874831086099</v>
+        <v>0.02785774311880107</v>
       </c>
       <c r="M7" t="n">
-        <v>4.398977287778727</v>
+        <v>4.398909105159279</v>
       </c>
       <c r="N7" t="n">
-        <v>28.56711572989578</v>
+        <v>28.54709749150962</v>
       </c>
       <c r="O7" t="n">
-        <v>5.344821393638498</v>
+        <v>5.34294838937357</v>
       </c>
       <c r="P7" t="n">
-        <v>371.3153160776878</v>
+        <v>371.2878357709362</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17867,28 +17913,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1652179212778972</v>
+        <v>-0.1661934001444908</v>
       </c>
       <c r="J8" t="n">
+        <v>362</v>
+      </c>
+      <c r="K8" t="n">
         <v>361</v>
       </c>
-      <c r="K8" t="n">
-        <v>360</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.05116076758503907</v>
+        <v>0.05203165270338472</v>
       </c>
       <c r="M8" t="n">
-        <v>4.344903756551721</v>
+        <v>4.337261277210509</v>
       </c>
       <c r="N8" t="n">
-        <v>27.7293910249379</v>
+        <v>27.66082566705471</v>
       </c>
       <c r="O8" t="n">
-        <v>5.26587039575965</v>
+        <v>5.259356012579364</v>
       </c>
       <c r="P8" t="n">
-        <v>366.495828564366</v>
+        <v>366.5060928806561</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -17949,28 +17995,28 @@
         <v>0.1442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1343676774118439</v>
+        <v>-0.1352140857285447</v>
       </c>
       <c r="J9" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K9" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03921218118365244</v>
+        <v>0.039918800948199</v>
       </c>
       <c r="M9" t="n">
-        <v>3.958883883231866</v>
+        <v>3.952149960776888</v>
       </c>
       <c r="N9" t="n">
-        <v>24.45393973823878</v>
+        <v>24.39268090176746</v>
       </c>
       <c r="O9" t="n">
-        <v>4.945092490362417</v>
+        <v>4.938894704462473</v>
       </c>
       <c r="P9" t="n">
-        <v>370.6905900781457</v>
+        <v>370.6994378653164</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -18012,7 +18058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J362"/>
+  <dimension ref="A1:J363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36827,6 +36873,58 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-36.82715213695923,175.71492534782377</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-36.82780713881467,175.7153051874166</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-36.82845597467577,175.71569371487104</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-36.82908255046245,175.71611413671903</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-36.82968181272951,175.71659009219016</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-36.83021509879832,175.7171602139796</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-36.830746062314226,175.71776122047447</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-36.83111294041211,175.71853373446984</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0177/nzd0177.xlsx
+++ b/data/nzd0177/nzd0177.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J363"/>
+  <dimension ref="A1:J364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13504,6 +13504,42 @@
         <v>365.6</v>
       </c>
       <c r="J363" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>371.56</v>
+      </c>
+      <c r="C364" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="D364" t="n">
+        <v>368.68</v>
+      </c>
+      <c r="E364" t="n">
+        <v>371.11</v>
+      </c>
+      <c r="F364" t="n">
+        <v>370.36</v>
+      </c>
+      <c r="G364" t="n">
+        <v>373.68</v>
+      </c>
+      <c r="H364" t="n">
+        <v>362.37</v>
+      </c>
+      <c r="I364" t="n">
+        <v>367.64</v>
+      </c>
+      <c r="J364" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13520,7 +13556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B373"/>
+  <dimension ref="A1:B374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17253,6 +17289,16 @@
       </c>
       <c r="B373" t="n">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>-0.43</v>
       </c>
     </row>
   </sheetData>
@@ -17421,28 +17467,28 @@
         <v>0.1672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3286198869067201</v>
+        <v>0.3284343825087408</v>
       </c>
       <c r="J2" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K2" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1774792004119369</v>
+        <v>0.178229228228139</v>
       </c>
       <c r="M2" t="n">
-        <v>4.195335440776939</v>
+        <v>4.184449327687826</v>
       </c>
       <c r="N2" t="n">
-        <v>27.76337726330272</v>
+        <v>27.6871987164979</v>
       </c>
       <c r="O2" t="n">
-        <v>5.269096437085083</v>
+        <v>5.261862666062076</v>
       </c>
       <c r="P2" t="n">
-        <v>363.132196866952</v>
+        <v>363.1341395792632</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17503,28 +17549,28 @@
         <v>0.1707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2560334287717259</v>
+        <v>0.2575883132890983</v>
       </c>
       <c r="J3" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K3" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1802474924724576</v>
+        <v>0.1827853388234463</v>
       </c>
       <c r="M3" t="n">
-        <v>3.169651104549347</v>
+        <v>3.169801790407369</v>
       </c>
       <c r="N3" t="n">
-        <v>16.53834517388024</v>
+        <v>16.51418421768624</v>
       </c>
       <c r="O3" t="n">
-        <v>4.066736427884187</v>
+        <v>4.063764783754866</v>
       </c>
       <c r="P3" t="n">
-        <v>358.7855374805955</v>
+        <v>358.7692538057749</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17585,28 +17631,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2175680834773</v>
+        <v>0.2185889129586094</v>
       </c>
       <c r="J4" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K4" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1413995217425364</v>
+        <v>0.1432367822116818</v>
       </c>
       <c r="M4" t="n">
-        <v>3.093123409921132</v>
+        <v>3.08969112138783</v>
       </c>
       <c r="N4" t="n">
-        <v>15.94478776982568</v>
+        <v>15.9100864977668</v>
       </c>
       <c r="O4" t="n">
-        <v>3.993092507045847</v>
+        <v>3.988744977780204</v>
       </c>
       <c r="P4" t="n">
-        <v>361.046916972586</v>
+        <v>361.0362262395218</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17667,28 +17713,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.122618668169945</v>
+        <v>0.1229391682492946</v>
       </c>
       <c r="J5" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K5" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06528464441947313</v>
+        <v>0.06598462873492073</v>
       </c>
       <c r="M5" t="n">
-        <v>2.782236206493645</v>
+        <v>2.77605788680376</v>
       </c>
       <c r="N5" t="n">
-        <v>11.94171518924773</v>
+        <v>11.90972709927112</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45567868721149</v>
+        <v>3.451047246745707</v>
       </c>
       <c r="P5" t="n">
-        <v>367.2610893650231</v>
+        <v>367.257732897701</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -17749,28 +17795,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03257734508696567</v>
+        <v>0.03352890826472249</v>
       </c>
       <c r="J6" t="n">
+        <v>363</v>
+      </c>
+      <c r="K6" t="n">
         <v>362</v>
       </c>
-      <c r="K6" t="n">
-        <v>361</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.002561507041678901</v>
+        <v>0.002729060058389354</v>
       </c>
       <c r="M6" t="n">
-        <v>3.640104496939608</v>
+        <v>3.634359245029738</v>
       </c>
       <c r="N6" t="n">
-        <v>22.71607659948119</v>
+        <v>22.66123250141809</v>
       </c>
       <c r="O6" t="n">
-        <v>4.766138541784239</v>
+        <v>4.760381549982951</v>
       </c>
       <c r="P6" t="n">
-        <v>367.7887137435646</v>
+        <v>367.7786827750476</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -17831,28 +17877,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1219925597992143</v>
+        <v>-0.1188354102865441</v>
       </c>
       <c r="J7" t="n">
+        <v>363</v>
+      </c>
+      <c r="K7" t="n">
         <v>362</v>
       </c>
-      <c r="K7" t="n">
-        <v>361</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02785774311880107</v>
+        <v>0.02655589179015383</v>
       </c>
       <c r="M7" t="n">
-        <v>4.398909105159279</v>
+        <v>4.401310111912313</v>
       </c>
       <c r="N7" t="n">
-        <v>28.54709749150962</v>
+        <v>28.55528513558513</v>
       </c>
       <c r="O7" t="n">
-        <v>5.34294838937357</v>
+        <v>5.34371454473245</v>
       </c>
       <c r="P7" t="n">
-        <v>371.2878357709362</v>
+        <v>371.2545544627633</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17913,28 +17959,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1661934001444908</v>
+        <v>-0.1660281450066529</v>
       </c>
       <c r="J8" t="n">
+        <v>363</v>
+      </c>
+      <c r="K8" t="n">
         <v>362</v>
       </c>
-      <c r="K8" t="n">
-        <v>361</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.05203165270338472</v>
+        <v>0.05224407501685302</v>
       </c>
       <c r="M8" t="n">
-        <v>4.337261277210509</v>
+        <v>4.326156843639724</v>
       </c>
       <c r="N8" t="n">
-        <v>27.66082566705471</v>
+        <v>27.58465303830795</v>
       </c>
       <c r="O8" t="n">
-        <v>5.259356012579364</v>
+        <v>5.252109389408027</v>
       </c>
       <c r="P8" t="n">
-        <v>366.5060928806561</v>
+        <v>366.5043508322839</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -17995,28 +18041,28 @@
         <v>0.1442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1352140857285447</v>
+        <v>-0.1349122177128192</v>
       </c>
       <c r="J9" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K9" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L9" t="n">
-        <v>0.039918800948199</v>
+        <v>0.03998655781437377</v>
       </c>
       <c r="M9" t="n">
-        <v>3.952149960776888</v>
+        <v>3.942741739154234</v>
       </c>
       <c r="N9" t="n">
-        <v>24.39268090176746</v>
+        <v>24.32628999233166</v>
       </c>
       <c r="O9" t="n">
-        <v>4.938894704462473</v>
+        <v>4.932168893329957</v>
       </c>
       <c r="P9" t="n">
-        <v>370.6994378653164</v>
+        <v>370.6962765240388</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -18058,7 +18104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J363"/>
+  <dimension ref="A1:J364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36925,6 +36971,58 @@
         </is>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>-36.827149575182105,175.71493114041058</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>-36.82780086285317,175.71532019927457</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>-36.828451558693885,175.71570462412961</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-36.82907902769983,175.71612143918352</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-36.82967345888962,175.71660400963316</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-36.830208419693776,175.71716838629996</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-36.8307314266622,175.71777429039818</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-36.831097598563204,175.7185463184361</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0177/nzd0177.xlsx
+++ b/data/nzd0177/nzd0177.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J364"/>
+  <dimension ref="A1:J366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13542,6 +13542,78 @@
       <c r="J364" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>371.07</v>
+      </c>
+      <c r="C365" t="n">
+        <v>368.64</v>
+      </c>
+      <c r="D365" t="n">
+        <v>369.34</v>
+      </c>
+      <c r="E365" t="n">
+        <v>372.51</v>
+      </c>
+      <c r="F365" t="n">
+        <v>372.38</v>
+      </c>
+      <c r="G365" t="n">
+        <v>374.67</v>
+      </c>
+      <c r="H365" t="n">
+        <v>364.56</v>
+      </c>
+      <c r="I365" t="n">
+        <v>369.87</v>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>369.12</v>
+      </c>
+      <c r="C366" t="n">
+        <v>366.55</v>
+      </c>
+      <c r="D366" t="n">
+        <v>368.03</v>
+      </c>
+      <c r="E366" t="n">
+        <v>371.66</v>
+      </c>
+      <c r="F366" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="G366" t="n">
+        <v>374.55</v>
+      </c>
+      <c r="H366" t="n">
+        <v>364.99</v>
+      </c>
+      <c r="I366" t="n">
+        <v>369.33</v>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13556,7 +13628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B374"/>
+  <dimension ref="A1:B376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17299,6 +17371,26 @@
       </c>
       <c r="B374" t="n">
         <v>-0.43</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -17467,28 +17559,28 @@
         <v>0.1672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3284343825087408</v>
+        <v>0.3263775348830543</v>
       </c>
       <c r="J2" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K2" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L2" t="n">
-        <v>0.178229228228139</v>
+        <v>0.178127118413016</v>
       </c>
       <c r="M2" t="n">
-        <v>4.184449327687826</v>
+        <v>4.168975772666784</v>
       </c>
       <c r="N2" t="n">
-        <v>27.6871987164979</v>
+        <v>27.55927653939067</v>
       </c>
       <c r="O2" t="n">
-        <v>5.261862666062076</v>
+        <v>5.249692994775092</v>
       </c>
       <c r="P2" t="n">
-        <v>363.1341395792632</v>
+        <v>363.1558517949292</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17549,28 +17641,28 @@
         <v>0.1707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2575883132890983</v>
+        <v>0.259706876139093</v>
       </c>
       <c r="J3" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K3" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1827853388234463</v>
+        <v>0.1869364299617232</v>
       </c>
       <c r="M3" t="n">
-        <v>3.169801790407369</v>
+        <v>3.164372827107774</v>
       </c>
       <c r="N3" t="n">
-        <v>16.51418421768624</v>
+        <v>16.44940310350584</v>
       </c>
       <c r="O3" t="n">
-        <v>4.063764783754866</v>
+        <v>4.055786373011508</v>
       </c>
       <c r="P3" t="n">
-        <v>358.7692538057749</v>
+        <v>358.7469010277478</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17631,28 +17723,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2185889129586094</v>
+        <v>0.2205594265659569</v>
       </c>
       <c r="J4" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K4" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1432367822116818</v>
+        <v>0.1468897899996785</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08969112138783</v>
+        <v>3.082402812489121</v>
       </c>
       <c r="N4" t="n">
-        <v>15.9100864977668</v>
+        <v>15.84227202039928</v>
       </c>
       <c r="O4" t="n">
-        <v>3.988744977780204</v>
+        <v>3.980235171494177</v>
       </c>
       <c r="P4" t="n">
-        <v>361.0362262395218</v>
+        <v>361.0154338200317</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17713,28 +17805,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1229391682492946</v>
+        <v>0.1246348228787686</v>
       </c>
       <c r="J5" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K5" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06598462873492073</v>
+        <v>0.06842808700909264</v>
       </c>
       <c r="M5" t="n">
-        <v>2.77605788680376</v>
+        <v>2.768540970137998</v>
       </c>
       <c r="N5" t="n">
-        <v>11.90972709927112</v>
+        <v>11.85805546118228</v>
       </c>
       <c r="O5" t="n">
-        <v>3.451047246745707</v>
+        <v>3.44355273826063</v>
       </c>
       <c r="P5" t="n">
-        <v>367.257732897701</v>
+        <v>367.2398399988371</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -17795,28 +17887,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03352890826472249</v>
+        <v>0.03743213056178955</v>
       </c>
       <c r="J6" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K6" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002729060058389354</v>
+        <v>0.003432728497050341</v>
       </c>
       <c r="M6" t="n">
-        <v>3.634359245029738</v>
+        <v>3.631668897629779</v>
       </c>
       <c r="N6" t="n">
-        <v>22.66123250141809</v>
+        <v>22.60274230095601</v>
       </c>
       <c r="O6" t="n">
-        <v>4.760381549982951</v>
+        <v>4.754234144523807</v>
       </c>
       <c r="P6" t="n">
-        <v>367.7786827750476</v>
+        <v>367.7372223389509</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -17877,28 +17969,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1188354102865441</v>
+        <v>-0.1115238251641747</v>
       </c>
       <c r="J7" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K7" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02655589179015383</v>
+        <v>0.02357062551995592</v>
       </c>
       <c r="M7" t="n">
-        <v>4.401310111912313</v>
+        <v>4.410490665762016</v>
       </c>
       <c r="N7" t="n">
-        <v>28.55528513558513</v>
+        <v>28.62924640995414</v>
       </c>
       <c r="O7" t="n">
-        <v>5.34371454473245</v>
+        <v>5.350630468454549</v>
       </c>
       <c r="P7" t="n">
-        <v>371.2545544627633</v>
+        <v>371.176888318383</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17959,28 +18051,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1660281450066529</v>
+        <v>-0.16298037262182</v>
       </c>
       <c r="J8" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K8" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05224407501685302</v>
+        <v>0.05098421030003575</v>
       </c>
       <c r="M8" t="n">
-        <v>4.326156843639724</v>
+        <v>4.318223883213215</v>
       </c>
       <c r="N8" t="n">
-        <v>27.58465303830795</v>
+        <v>27.47345184343244</v>
       </c>
       <c r="O8" t="n">
-        <v>5.252109389408027</v>
+        <v>5.241512362232148</v>
       </c>
       <c r="P8" t="n">
-        <v>366.5043508322839</v>
+        <v>366.4719750666538</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -18041,28 +18133,28 @@
         <v>0.1442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1349122177128192</v>
+        <v>-0.1321144898437691</v>
       </c>
       <c r="J9" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K9" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03998655781437377</v>
+        <v>0.03882786838803742</v>
       </c>
       <c r="M9" t="n">
-        <v>3.942741739154234</v>
+        <v>3.934620037958912</v>
       </c>
       <c r="N9" t="n">
-        <v>24.32628999233166</v>
+        <v>24.22764570517691</v>
       </c>
       <c r="O9" t="n">
-        <v>4.932168893329957</v>
+        <v>4.92215864282907</v>
       </c>
       <c r="P9" t="n">
-        <v>370.6962765240388</v>
+        <v>370.6667520040709</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -18104,7 +18196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J364"/>
+  <dimension ref="A1:J366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37023,6 +37115,110 @@
         </is>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>-36.82715170275974,175.71492632961818</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>-36.82779990691185,175.71532248584876</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>-36.82844888479612,175.71571122973506</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-36.829072538399146,175.71613489109</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-36.829662571947615,175.71662214719942</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-36.83020206169955,175.71717616571894</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-36.83071540062176,175.71778860195906</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-36.83108082781525,175.71856007443284</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>-36.82716016964852,175.71490718462525</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>-36.82780859350747,175.71530170784652</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>-36.82845419207768,175.71569811860857</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-36.82907647833188,175.71612672386135</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>-36.829664781673685,175.71661846581264</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>-36.830202832365536,175.71717522275915</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-36.83071225395611,175.71779141199087</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-36.83108488889336,175.71855674338485</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0177/nzd0177.xlsx
+++ b/data/nzd0177/nzd0177.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J366"/>
+  <dimension ref="A1:J368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13612,6 +13612,78 @@
         <v>369.33</v>
       </c>
       <c r="J366" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>369.15</v>
+      </c>
+      <c r="C367" t="n">
+        <v>366.58</v>
+      </c>
+      <c r="D367" t="n">
+        <v>369.41</v>
+      </c>
+      <c r="E367" t="n">
+        <v>372.73</v>
+      </c>
+      <c r="F367" t="n">
+        <v>373.75</v>
+      </c>
+      <c r="G367" t="n">
+        <v>375.26</v>
+      </c>
+      <c r="H367" t="n">
+        <v>365.67</v>
+      </c>
+      <c r="I367" t="n">
+        <v>369.51</v>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>368.43</v>
+      </c>
+      <c r="C368" t="n">
+        <v>365.47</v>
+      </c>
+      <c r="D368" t="n">
+        <v>368</v>
+      </c>
+      <c r="E368" t="n">
+        <v>371.29</v>
+      </c>
+      <c r="F368" t="n">
+        <v>373.32</v>
+      </c>
+      <c r="G368" t="n">
+        <v>375.29</v>
+      </c>
+      <c r="H368" t="n">
+        <v>367.08</v>
+      </c>
+      <c r="I368" t="n">
+        <v>370.83</v>
+      </c>
+      <c r="J368" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13628,7 +13700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B376"/>
+  <dimension ref="A1:B378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17391,6 +17463,26 @@
       </c>
       <c r="B376" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -17559,28 +17651,28 @@
         <v>0.1672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3263775348830543</v>
+        <v>0.3229230827298532</v>
       </c>
       <c r="J2" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K2" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L2" t="n">
-        <v>0.178127118413016</v>
+        <v>0.1765745661118064</v>
       </c>
       <c r="M2" t="n">
-        <v>4.168975772666784</v>
+        <v>4.158812921096131</v>
       </c>
       <c r="N2" t="n">
-        <v>27.55927653939067</v>
+        <v>27.46292799198241</v>
       </c>
       <c r="O2" t="n">
-        <v>5.249692994775092</v>
+        <v>5.240508371521069</v>
       </c>
       <c r="P2" t="n">
-        <v>363.1558517949292</v>
+        <v>363.1924268714994</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17641,28 +17733,28 @@
         <v>0.1707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.259706876139093</v>
+        <v>0.2600205030956219</v>
       </c>
       <c r="J3" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K3" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1869364299617232</v>
+        <v>0.1892091231354472</v>
       </c>
       <c r="M3" t="n">
-        <v>3.164372827107774</v>
+        <v>3.150424349944955</v>
       </c>
       <c r="N3" t="n">
-        <v>16.44940310350584</v>
+        <v>16.36192877738137</v>
       </c>
       <c r="O3" t="n">
-        <v>4.055786373011508</v>
+        <v>4.044988105962905</v>
       </c>
       <c r="P3" t="n">
-        <v>358.7469010277478</v>
+        <v>358.7435866668688</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17723,28 +17815,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2205594265659569</v>
+        <v>0.2224796891085909</v>
       </c>
       <c r="J4" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K4" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1468897899996785</v>
+        <v>0.1505254926761838</v>
       </c>
       <c r="M4" t="n">
-        <v>3.082402812489121</v>
+        <v>3.07503609315953</v>
       </c>
       <c r="N4" t="n">
-        <v>15.84227202039928</v>
+        <v>15.77515227018201</v>
       </c>
       <c r="O4" t="n">
-        <v>3.980235171494177</v>
+        <v>3.971794590633056</v>
       </c>
       <c r="P4" t="n">
-        <v>361.0154338200317</v>
+        <v>360.9951120603711</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17805,28 +17897,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1246348228787686</v>
+        <v>0.1261804650324932</v>
       </c>
       <c r="J5" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K5" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06842808700909264</v>
+        <v>0.07076600143349854</v>
       </c>
       <c r="M5" t="n">
-        <v>2.768540970137998</v>
+        <v>2.760386616320351</v>
       </c>
       <c r="N5" t="n">
-        <v>11.85805546118228</v>
+        <v>11.80693604487169</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44355273826063</v>
+        <v>3.436122239512396</v>
       </c>
       <c r="P5" t="n">
-        <v>367.2398399988371</v>
+        <v>367.2234843339543</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -17887,28 +17979,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03743213056178955</v>
+        <v>0.04272293098979737</v>
       </c>
       <c r="J6" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K6" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003432728497050341</v>
+        <v>0.004499134896511769</v>
       </c>
       <c r="M6" t="n">
-        <v>3.631668897629779</v>
+        <v>3.635514791128943</v>
       </c>
       <c r="N6" t="n">
-        <v>22.60274230095601</v>
+        <v>22.6025082960923</v>
       </c>
       <c r="O6" t="n">
-        <v>4.754234144523807</v>
+        <v>4.754209534306654</v>
       </c>
       <c r="P6" t="n">
-        <v>367.7372223389509</v>
+        <v>367.6808485468923</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -17969,28 +18061,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1115238251641747</v>
+        <v>-0.1036784371551065</v>
       </c>
       <c r="J7" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K7" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02357062551995592</v>
+        <v>0.02050062762235449</v>
       </c>
       <c r="M7" t="n">
-        <v>4.410490665762016</v>
+        <v>4.423087259341401</v>
       </c>
       <c r="N7" t="n">
-        <v>28.62924640995414</v>
+        <v>28.74324654150772</v>
       </c>
       <c r="O7" t="n">
-        <v>5.350630468454549</v>
+        <v>5.361272847142525</v>
       </c>
       <c r="P7" t="n">
-        <v>371.176888318383</v>
+        <v>371.0932916173415</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -18051,28 +18143,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.16298037262182</v>
+        <v>-0.1582351760999512</v>
       </c>
       <c r="J8" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K8" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05098421030003575</v>
+        <v>0.04861164069580082</v>
       </c>
       <c r="M8" t="n">
-        <v>4.318223883213215</v>
+        <v>4.319227039434643</v>
       </c>
       <c r="N8" t="n">
-        <v>27.47345184343244</v>
+        <v>27.42493168791926</v>
       </c>
       <c r="O8" t="n">
-        <v>5.241512362232148</v>
+        <v>5.236881866905082</v>
       </c>
       <c r="P8" t="n">
-        <v>366.4719750666538</v>
+        <v>366.421405167506</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -18133,28 +18225,28 @@
         <v>0.1442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1321144898437691</v>
+        <v>-0.1287558758532343</v>
       </c>
       <c r="J9" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K9" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03882786838803742</v>
+        <v>0.03732350785751726</v>
       </c>
       <c r="M9" t="n">
-        <v>3.934620037958912</v>
+        <v>3.929249796998674</v>
       </c>
       <c r="N9" t="n">
-        <v>24.22764570517691</v>
+        <v>24.14818846095735</v>
       </c>
       <c r="O9" t="n">
-        <v>4.92215864282907</v>
+        <v>4.914080632321508</v>
       </c>
       <c r="P9" t="n">
-        <v>370.6667520040709</v>
+        <v>370.6311884128236</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -18196,7 +18288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J366"/>
+  <dimension ref="A1:J368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37219,6 +37311,110 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>-36.82716003938871,175.71490747916363</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>-36.82780846881953,175.71530200609538</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>-36.82844860120089,175.71571193032955</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-36.82907151865176,175.71613700496084</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-36.82965518822807,175.71663444841712</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-36.83019827259167,175.71718080193773</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-36.83070727783357,175.71779585576164</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-36.831083535200655,175.7185578537342</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>-36.827163165623844,175.71490041024208</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>-36.827813082273245,175.7152909708865</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>-36.82845431361847,175.71569781835376</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>-36.82907819336125,175.71612316871452</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>-36.829657505746006,175.71663058745125</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>-36.830198079925154,175.71718103767765</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-36.83069695969664,175.7178050700492</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>-36.83107360812064,175.71856599629507</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
